--- a/data/trans_orig/P04D_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04D_R-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2012</t>
+          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11424</t>
+          <t>10946</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30622</t>
+          <t>32041</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21589</t>
+          <t>23036</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20085</t>
+          <t>20276</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46421</t>
+          <t>44749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>183860</t>
+          <t>186281</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>228302</t>
+          <t>228025</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130094</t>
+          <t>131022</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>167405</t>
+          <t>167159</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>325027</t>
+          <t>325423</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>384524</t>
+          <t>382990</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,95%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>190578</t>
+          <t>188545</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>234974</t>
+          <t>232656</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135581</t>
+          <t>136135</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>174272</t>
+          <t>172168</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>338659</t>
+          <t>341146</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>396884</t>
+          <t>399162</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>53,1%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16560</t>
+          <t>17042</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>10030</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26488</t>
+          <t>26642</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16967</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37489</t>
+          <t>37334</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>203426</t>
+          <t>206088</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>248733</t>
+          <t>248872</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>172544</t>
+          <t>172055</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>210787</t>
+          <t>212811</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>392131</t>
+          <t>391339</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>448763</t>
+          <t>448790</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>161563</t>
+          <t>160542</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>205866</t>
+          <t>203449</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110974</t>
+          <t>109409</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>148600</t>
+          <t>149313</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>283372</t>
+          <t>280530</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>339083</t>
+          <t>338728</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,76%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15867</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36501</t>
+          <t>36453</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23925</t>
+          <t>22972</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28817</t>
+          <t>28460</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>54002</t>
+          <t>52941</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>376109</t>
+          <t>374632</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>426702</t>
+          <t>426216</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145528</t>
+          <t>145548</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>177262</t>
+          <t>178602</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>537031</t>
+          <t>538310</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>593983</t>
+          <t>595203</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,91%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>178176</t>
+          <t>180193</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>227469</t>
+          <t>230667</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66809</t>
+          <t>67110</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>98500</t>
+          <t>99553</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>258280</t>
+          <t>255564</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>313791</t>
+          <t>312440</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40827</t>
+          <t>40220</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68946</t>
+          <t>68845</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24560</t>
+          <t>24918</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50699</t>
+          <t>51205</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72644</t>
+          <t>72957</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111950</t>
+          <t>112115</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>757723</t>
+          <t>757603</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>823318</t>
+          <t>822084</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>462425</t>
+          <t>460094</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>517891</t>
+          <t>516931</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1238576</t>
+          <t>1241725</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1322511</t>
+          <t>1325024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,81%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>282380</t>
+          <t>283381</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>344320</t>
+          <t>343276</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>214595</t>
+          <t>216331</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>266952</t>
+          <t>268549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>513322</t>
+          <t>513066</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>595132</t>
+          <t>593905</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16105</t>
+          <t>16058</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35322</t>
+          <t>35691</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19858</t>
+          <t>21023</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42062</t>
+          <t>44081</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42347</t>
+          <t>41778</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72029</t>
+          <t>72421</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>356308</t>
+          <t>357524</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>395626</t>
+          <t>398694</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>503054</t>
+          <t>506208</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>557231</t>
+          <t>555591</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>874380</t>
+          <t>876961</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>940918</t>
+          <t>943239</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,15%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91512</t>
+          <t>89611</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129689</t>
+          <t>128382</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>175640</t>
+          <t>176546</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>228622</t>
+          <t>226455</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>276103</t>
+          <t>276097</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>342535</t>
+          <t>337612</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20200</t>
+          <t>20214</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36461</t>
+          <t>38074</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64208</t>
+          <t>66304</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>47813</t>
+          <t>46698</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>77221</t>
+          <t>78268</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>131677</t>
+          <t>131234</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>163863</t>
+          <t>163391</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>732439</t>
+          <t>731844</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>795744</t>
+          <t>793375</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>877764</t>
+          <t>874740</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>945464</t>
+          <t>947035</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,81%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>92705</t>
+          <t>93768</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>124590</t>
+          <t>126204</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>266915</t>
+          <t>268467</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>324887</t>
+          <t>325644</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>372197</t>
+          <t>371997</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>438956</t>
+          <t>439504</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>119482</t>
+          <t>119785</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>168572</t>
+          <t>169017</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>135471</t>
+          <t>134490</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>187346</t>
+          <t>186792</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>269635</t>
+          <t>264551</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>336590</t>
+          <t>337564</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2095374</t>
+          <t>2095665</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2208207</t>
+          <t>2207902</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2225662</t>
+          <t>2230983</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2348878</t>
+          <t>2348128</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4352552</t>
+          <t>4352520</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4517929</t>
+          <t>4528322</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,95%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1068778</t>
+          <t>1072578</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1180819</t>
+          <t>1183988</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1043046</t>
+          <t>1052177</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1157437</t>
+          <t>1160145</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2152495</t>
+          <t>2142632</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2314216</t>
+          <t>2303558</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2016</t>
+          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31095</t>
+          <t>31532</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58650</t>
+          <t>57933</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22932</t>
+          <t>23615</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45922</t>
+          <t>46486</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59763</t>
+          <t>60918</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96480</t>
+          <t>95881</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>182066</t>
+          <t>181858</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>223884</t>
+          <t>224064</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125950</t>
+          <t>126328</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>164296</t>
+          <t>163546</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>317020</t>
+          <t>316165</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>374656</t>
+          <t>375258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>162255</t>
+          <t>162309</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>202941</t>
+          <t>203998</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>149913</t>
+          <t>151198</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>189254</t>
+          <t>188202</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>323905</t>
+          <t>327066</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>384396</t>
+          <t>382666</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,3%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>28897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54539</t>
+          <t>54034</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24941</t>
+          <t>24671</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49158</t>
+          <t>46270</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58869</t>
+          <t>59662</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>94364</t>
+          <t>93903</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>175195</t>
+          <t>175130</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>214734</t>
+          <t>215223</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>160929</t>
+          <t>162370</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>201853</t>
+          <t>200551</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>347843</t>
+          <t>345809</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>405629</t>
+          <t>404505</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,97%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122911</t>
+          <t>123995</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>161470</t>
+          <t>163322</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>137681</t>
+          <t>137357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>177871</t>
+          <t>175452</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>269302</t>
+          <t>268714</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>326722</t>
+          <t>325557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62901</t>
+          <t>61948</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95786</t>
+          <t>95650</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24418</t>
+          <t>22963</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>76820</t>
+          <t>73813</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>114677</t>
+          <t>112529</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>249959</t>
+          <t>251981</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>296829</t>
+          <t>295964</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78243</t>
+          <t>79359</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105093</t>
+          <t>104649</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>339516</t>
+          <t>339690</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>391549</t>
+          <t>392969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,11%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147643</t>
+          <t>147954</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>190486</t>
+          <t>189251</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47119</t>
+          <t>47482</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71910</t>
+          <t>72916</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>201759</t>
+          <t>201823</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>254467</t>
+          <t>253526</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>165749</t>
+          <t>162825</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>216110</t>
+          <t>216215</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>106219</t>
+          <t>107843</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>148497</t>
+          <t>147801</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>283068</t>
+          <t>282206</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>351474</t>
+          <t>348972</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>591014</t>
+          <t>590968</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>659995</t>
+          <t>660688</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>403937</t>
+          <t>403853</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>459808</t>
+          <t>460498</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1015941</t>
+          <t>1014599</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1103681</t>
+          <t>1102584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,81%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>303720</t>
+          <t>306464</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>368362</t>
+          <t>369029</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>242021</t>
+          <t>240580</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>294104</t>
+          <t>294265</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>566861</t>
+          <t>565858</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>648407</t>
+          <t>649189</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110699</t>
+          <t>112444</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>152629</t>
+          <t>153939</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109135</t>
+          <t>108100</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>150697</t>
+          <t>152385</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>233659</t>
+          <t>231252</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>293407</t>
+          <t>293705</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>333012</t>
+          <t>334336</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>384492</t>
+          <t>384487</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>412481</t>
+          <t>413078</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>466655</t>
+          <t>468089</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>762375</t>
+          <t>758922</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>837111</t>
+          <t>833178</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,31%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>108940</t>
+          <t>109481</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153089</t>
+          <t>149358</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>147706</t>
+          <t>146360</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>193885</t>
+          <t>192211</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>265051</t>
+          <t>267279</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>330116</t>
+          <t>328265</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34813</t>
+          <t>35145</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59740</t>
+          <t>59473</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>153688</t>
+          <t>149233</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>206020</t>
+          <t>204334</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>195286</t>
+          <t>198539</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>252198</t>
+          <t>253560</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>119118</t>
+          <t>120583</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>154343</t>
+          <t>152448</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>515775</t>
+          <t>516655</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>585790</t>
+          <t>584710</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>642349</t>
+          <t>645362</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>719644</t>
+          <t>721123</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,67%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>87878</t>
+          <t>88727</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>120923</t>
+          <t>120655</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>326225</t>
+          <t>328470</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>389794</t>
+          <t>389488</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>426084</t>
+          <t>426151</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>498948</t>
+          <t>496395</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>486038</t>
+          <t>486029</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>576785</t>
+          <t>570879</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>475688</t>
+          <t>473840</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>561346</t>
+          <t>559848</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>981727</t>
+          <t>984070</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1104254</t>
+          <t>1108861</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1733882</t>
+          <t>1734553</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1849534</t>
+          <t>1847394</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1778626</t>
+          <t>1774172</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1899058</t>
+          <t>1899548</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3543131</t>
+          <t>3555710</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3711417</t>
+          <t>3725138</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,85%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1003191</t>
+          <t>1014252</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1112214</t>
+          <t>1121200</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1119659</t>
+          <t>1119341</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1236509</t>
+          <t>1236494</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2160104</t>
+          <t>2167094</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2323703</t>
+          <t>2320075</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2023</t>
+          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31335</t>
+          <t>30972</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58109</t>
+          <t>57851</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38997</t>
+          <t>38641</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65582</t>
+          <t>64362</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76268</t>
+          <t>77038</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111637</t>
+          <t>113056</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>239335</t>
+          <t>238866</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284470</t>
+          <t>284653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>204228</t>
+          <t>205248</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>242385</t>
+          <t>242837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>458832</t>
+          <t>458724</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>515017</t>
+          <t>515370</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>176509</t>
+          <t>176283</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>223275</t>
+          <t>223938</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>155102</t>
+          <t>154130</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>191021</t>
+          <t>190667</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>343857</t>
+          <t>342641</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>398881</t>
+          <t>400330</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36963</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66041</t>
+          <t>66596</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38559</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61953</t>
+          <t>63158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>82500</t>
+          <t>82922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119583</t>
+          <t>119699</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>244280</t>
+          <t>244727</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>289974</t>
+          <t>289687</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>200809</t>
+          <t>199571</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>234175</t>
+          <t>232643</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>454570</t>
+          <t>456587</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>510670</t>
+          <t>512023</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,34%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>112845</t>
+          <t>113326</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155476</t>
+          <t>155138</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99703</t>
+          <t>102348</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130381</t>
+          <t>132469</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>225861</t>
+          <t>224472</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>277701</t>
+          <t>275419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>14679</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73983</t>
+          <t>75259</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15637</t>
+          <t>16069</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30742</t>
+          <t>31514</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25027</t>
+          <t>24989</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>99011</t>
+          <t>96620</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>101928</t>
+          <t>108902</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>447032</t>
+          <t>449218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94545</t>
+          <t>94605</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114921</t>
+          <t>115216</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159106</t>
+          <t>177102</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>549461</t>
+          <t>550842</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,96%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>153444</t>
+          <t>150310</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>549336</t>
+          <t>539352</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30813</t>
+          <t>30422</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50172</t>
+          <t>49387</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>194135</t>
+          <t>193857</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>648585</t>
+          <t>632451</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>75,73%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103592</t>
+          <t>102175</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>155820</t>
+          <t>152624</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45702</t>
+          <t>49755</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120017</t>
+          <t>119788</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>146998</t>
+          <t>148837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>252710</t>
+          <t>255229</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>672842</t>
+          <t>676989</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>743159</t>
+          <t>743503</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>619563</t>
+          <t>624252</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>831576</t>
+          <t>819341</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1334090</t>
+          <t>1329650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1619707</t>
+          <t>1615113</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,28%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>172331</t>
+          <t>176592</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>229485</t>
+          <t>231499</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>98588</t>
+          <t>102609</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>242740</t>
+          <t>242045</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>258562</t>
+          <t>252040</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>438339</t>
+          <t>440962</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49586</t>
+          <t>48915</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77418</t>
+          <t>79190</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78537</t>
+          <t>79463</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>337016</t>
+          <t>328806</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>138805</t>
+          <t>140223</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>408785</t>
+          <t>398304</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>312491</t>
+          <t>311427</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>354140</t>
+          <t>356162</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>415229</t>
+          <t>427557</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>636810</t>
+          <t>637030</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>743072</t>
+          <t>756188</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975163</t>
+          <t>972591</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,88%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61317</t>
+          <t>60806</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96098</t>
+          <t>96817</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>85483</t>
+          <t>89182</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>140103</t>
+          <t>143494</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>161800</t>
+          <t>159081</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>225971</t>
+          <t>225742</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12793</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50288</t>
+          <t>47585</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63258</t>
+          <t>62445</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>97712</t>
+          <t>96345</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>80897</t>
+          <t>82653</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>132552</t>
+          <t>130642</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>124710</t>
+          <t>124871</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>176859</t>
+          <t>176736</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>519936</t>
+          <t>521280</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>569836</t>
+          <t>568104</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>661671</t>
+          <t>658976</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>732399</t>
+          <t>731294</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,99%</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39466</t>
+          <t>40197</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>89166</t>
+          <t>89668</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>118096</t>
+          <t>119134</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>161135</t>
+          <t>161144</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>170135</t>
+          <t>172887</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>236074</t>
+          <t>237906</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>266748</t>
+          <t>270136</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>399284</t>
+          <t>399871</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>349642</t>
+          <t>346688</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>680601</t>
+          <t>652182</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>683233</t>
+          <t>672794</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1007785</t>
+          <t>1022303</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1552584</t>
+          <t>1469360</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2184842</t>
+          <t>2182380</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2227001</t>
+          <t>2239624</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2581118</t>
+          <t>2581603</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3836319</t>
+          <t>3866212</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4622026</t>
+          <t>4631363</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,61%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>814727</t>
+          <t>817937</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1563053</t>
+          <t>1675803</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>625760</t>
+          <t>626459</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>839168</t>
+          <t>839906</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1557530</t>
+          <t>1558119</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2398161</t>
+          <t>2442575</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04D_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04D_R-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10946</t>
+          <t>11241</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32041</t>
+          <t>31150</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23036</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20276</t>
+          <t>20480</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44749</t>
+          <t>48017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>186281</t>
+          <t>183203</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>228025</t>
+          <t>225820</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>131022</t>
+          <t>129992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>167159</t>
+          <t>167807</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>325423</t>
+          <t>323641</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>382990</t>
+          <t>381333</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,73%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>188545</t>
+          <t>189510</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>232656</t>
+          <t>232709</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136135</t>
+          <t>135997</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>172168</t>
+          <t>174242</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>341146</t>
+          <t>337490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>399162</t>
+          <t>396013</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,68%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17042</t>
+          <t>16929</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26642</t>
+          <t>26895</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16967</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37334</t>
+          <t>37433</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>206088</t>
+          <t>206880</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>248872</t>
+          <t>250668</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>172055</t>
+          <t>171943</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>212811</t>
+          <t>210360</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>391339</t>
+          <t>392743</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>448790</t>
+          <t>448713</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160542</t>
+          <t>160948</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203449</t>
+          <t>202908</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109409</t>
+          <t>112037</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149313</t>
+          <t>148609</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>280530</t>
+          <t>283772</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>338728</t>
+          <t>338500</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,73%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36453</t>
+          <t>37975</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22972</t>
+          <t>24036</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28460</t>
+          <t>27413</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52941</t>
+          <t>53028</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>374632</t>
+          <t>376638</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>426216</t>
+          <t>426383</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145548</t>
+          <t>146403</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178602</t>
+          <t>178859</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>538310</t>
+          <t>534766</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>595203</t>
+          <t>591401</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180193</t>
+          <t>179643</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>230667</t>
+          <t>227863</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67110</t>
+          <t>67134</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>99553</t>
+          <t>98160</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>255564</t>
+          <t>259679</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>312440</t>
+          <t>315355</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40220</t>
+          <t>40346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68845</t>
+          <t>69009</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24918</t>
+          <t>25002</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51205</t>
+          <t>50761</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72957</t>
+          <t>71360</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112115</t>
+          <t>110872</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>757603</t>
+          <t>756782</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>822084</t>
+          <t>821362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>460094</t>
+          <t>463978</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>516931</t>
+          <t>516731</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1241725</t>
+          <t>1239415</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1325024</t>
+          <t>1324429</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,78%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>283381</t>
+          <t>285639</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>343276</t>
+          <t>345599</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>216331</t>
+          <t>216421</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>268549</t>
+          <t>266658</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>513066</t>
+          <t>513668</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>593905</t>
+          <t>593702</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16058</t>
+          <t>16857</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35691</t>
+          <t>36712</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21023</t>
+          <t>21155</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44081</t>
+          <t>43405</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>41778</t>
+          <t>41942</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72421</t>
+          <t>72570</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>357524</t>
+          <t>354584</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>398694</t>
+          <t>396206</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>506208</t>
+          <t>503096</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>555591</t>
+          <t>556100</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>876961</t>
+          <t>877625</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>943239</t>
+          <t>942128</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,06%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>89611</t>
+          <t>91704</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128382</t>
+          <t>129193</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>176546</t>
+          <t>175121</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>226455</t>
+          <t>224579</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>276097</t>
+          <t>275953</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>337612</t>
+          <t>339507</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20214</t>
+          <t>21326</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38074</t>
+          <t>36435</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>66304</t>
+          <t>65172</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46698</t>
+          <t>45688</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>78268</t>
+          <t>77291</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>131234</t>
+          <t>131177</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>163391</t>
+          <t>162876</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>731844</t>
+          <t>733665</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>793375</t>
+          <t>795925</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>874740</t>
+          <t>876222</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>947035</t>
+          <t>944498</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,63%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>93768</t>
+          <t>93443</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>126204</t>
+          <t>124465</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>268467</t>
+          <t>266150</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>325644</t>
+          <t>327290</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>371997</t>
+          <t>371138</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>439504</t>
+          <t>440002</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>119785</t>
+          <t>119721</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>169017</t>
+          <t>169660</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>134490</t>
+          <t>134804</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>186792</t>
+          <t>185796</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>264551</t>
+          <t>270544</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>337564</t>
+          <t>340379</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2095665</t>
+          <t>2092706</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2207902</t>
+          <t>2212665</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2230983</t>
+          <t>2226703</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2348128</t>
+          <t>2347307</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4352520</t>
+          <t>4357714</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4528322</t>
+          <t>4525007</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,9%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1072578</t>
+          <t>1067361</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1183988</t>
+          <t>1181388</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1052177</t>
+          <t>1045058</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1160145</t>
+          <t>1158439</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2142632</t>
+          <t>2151440</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2303558</t>
+          <t>2313326</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31532</t>
+          <t>31598</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57933</t>
+          <t>59170</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23615</t>
+          <t>23386</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46486</t>
+          <t>46149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60918</t>
+          <t>61566</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95881</t>
+          <t>94136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>181858</t>
+          <t>181901</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>224064</t>
+          <t>223596</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126328</t>
+          <t>126422</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>163546</t>
+          <t>162339</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>316165</t>
+          <t>318946</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>375258</t>
+          <t>372794</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,03%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>162309</t>
+          <t>162663</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>203998</t>
+          <t>205251</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>151198</t>
+          <t>150634</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>188202</t>
+          <t>189331</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>327066</t>
+          <t>325251</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>382666</t>
+          <t>381402</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,14%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28897</t>
+          <t>29607</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54034</t>
+          <t>54951</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24671</t>
+          <t>24246</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46270</t>
+          <t>46967</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59662</t>
+          <t>60199</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>93903</t>
+          <t>95323</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>175130</t>
+          <t>175113</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>215223</t>
+          <t>215042</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>162370</t>
+          <t>160198</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>200551</t>
+          <t>201268</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,47 +4777,47 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
+          <t>54,06%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>376107</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>348695</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>403789</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>50,18%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>46,52%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>53,87%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>376107</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>345809</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>404505</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>50,18%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>46,14%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>53,97%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123995</t>
+          <t>122617</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>163322</t>
+          <t>161634</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>137357</t>
+          <t>137272</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>175452</t>
+          <t>176232</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>268714</t>
+          <t>269128</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>325557</t>
+          <t>325330</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61948</t>
+          <t>61932</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95650</t>
+          <t>96531</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22963</t>
+          <t>23334</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73813</t>
+          <t>75629</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112529</t>
+          <t>114438</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>251981</t>
+          <t>249846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>295964</t>
+          <t>297305</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79359</t>
+          <t>78733</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104649</t>
+          <t>104601</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>339690</t>
+          <t>342783</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>392969</t>
+          <t>395462</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,48%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147954</t>
+          <t>145233</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>189251</t>
+          <t>188806</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47482</t>
+          <t>47314</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72916</t>
+          <t>72697</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>201823</t>
+          <t>204428</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>253526</t>
+          <t>256693</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>162825</t>
+          <t>163803</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>216215</t>
+          <t>216619</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107843</t>
+          <t>108103</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>147801</t>
+          <t>149046</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>282206</t>
+          <t>281802</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>348972</t>
+          <t>351339</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>590968</t>
+          <t>592326</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>660688</t>
+          <t>661088</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>403853</t>
+          <t>404109</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>460498</t>
+          <t>462846</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1014599</t>
+          <t>1012512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1102584</t>
+          <t>1103172</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,84%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>306464</t>
+          <t>304091</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>369029</t>
+          <t>367434</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>240580</t>
+          <t>241856</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>294265</t>
+          <t>295399</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>565858</t>
+          <t>562154</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>649189</t>
+          <t>646223</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112444</t>
+          <t>113308</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>153939</t>
+          <t>154811</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>108100</t>
+          <t>109882</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>152385</t>
+          <t>152525</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>231252</t>
+          <t>232003</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>293705</t>
+          <t>290314</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>334336</t>
+          <t>334248</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>384487</t>
+          <t>384457</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>413078</t>
+          <t>413170</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>468089</t>
+          <t>466721</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>758922</t>
+          <t>762382</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>833178</t>
+          <t>836473</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>109481</t>
+          <t>108988</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>149358</t>
+          <t>150304</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>146360</t>
+          <t>145667</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>192211</t>
+          <t>192769</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>267279</t>
+          <t>270476</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>328265</t>
+          <t>330317</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35145</t>
+          <t>34631</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59473</t>
+          <t>59779</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>149233</t>
+          <t>155275</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>204334</t>
+          <t>204408</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>198539</t>
+          <t>196533</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>253560</t>
+          <t>253046</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>120583</t>
+          <t>119492</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>152448</t>
+          <t>154043</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>516655</t>
+          <t>514123</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>584710</t>
+          <t>582490</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>645362</t>
+          <t>646644</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>721123</t>
+          <t>721026</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,66%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>88727</t>
+          <t>88596</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>120655</t>
+          <t>122109</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>328470</t>
+          <t>325352</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>389488</t>
+          <t>388347</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>426151</t>
+          <t>426209</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>496395</t>
+          <t>497242</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>486029</t>
+          <t>487038</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>570879</t>
+          <t>573918</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>473840</t>
+          <t>474288</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>559848</t>
+          <t>561646</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>984070</t>
+          <t>980261</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1108861</t>
+          <t>1102442</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1734553</t>
+          <t>1731109</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1847394</t>
+          <t>1855102</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1774172</t>
+          <t>1775696</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1899548</t>
+          <t>1896121</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3555710</t>
+          <t>3547130</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3725138</t>
+          <t>3718919</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,76%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1014252</t>
+          <t>1011598</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1121200</t>
+          <t>1126030</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1119341</t>
+          <t>1123751</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1236494</t>
+          <t>1235367</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2167094</t>
+          <t>2163154</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2320075</t>
+          <t>2320769</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -7579,32 +7579,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>53468</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30972</t>
+          <t>39487</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57851</t>
+          <t>71683</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7614,32 +7614,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>49973</t>
+          <t>59775</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38641</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64362</t>
+          <t>75028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7649,32 +7649,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>93076</t>
+          <t>113244</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77038</t>
+          <t>94453</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113056</t>
+          <t>136135</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -7692,32 +7692,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>262416</t>
+          <t>286212</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>238866</t>
+          <t>261372</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284653</t>
+          <t>311246</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7727,32 +7727,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>224586</t>
+          <t>245328</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>205248</t>
+          <t>225050</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>242837</t>
+          <t>263705</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7762,32 +7762,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>487001</t>
+          <t>531540</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>458724</t>
+          <t>497092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>515370</t>
+          <t>565447</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,42%</t>
         </is>
       </c>
     </row>
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>199693</t>
+          <t>210938</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>176283</t>
+          <t>187729</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>223938</t>
+          <t>236096</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>172908</t>
+          <t>183308</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>154130</t>
+          <t>164336</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>190667</t>
+          <t>202706</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>372602</t>
+          <t>394245</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>342641</t>
+          <t>363890</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>400330</t>
+          <t>425248</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -7918,17 +7918,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7953,17 +7953,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7988,17 +7988,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8035,32 +8035,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>50286</t>
+          <t>55435</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36949</t>
+          <t>41656</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66596</t>
+          <t>72528</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8070,32 +8070,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>49846</t>
+          <t>55788</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38118</t>
+          <t>44252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63158</t>
+          <t>68976</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8105,32 +8105,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>100132</t>
+          <t>111223</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>82922</t>
+          <t>93394</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119699</t>
+          <t>132887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -8148,32 +8148,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>268235</t>
+          <t>289292</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>244727</t>
+          <t>264309</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>289687</t>
+          <t>310187</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8183,32 +8183,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>217527</t>
+          <t>238660</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>199571</t>
+          <t>221016</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>232643</t>
+          <t>256170</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8218,32 +8218,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>485762</t>
+          <t>527951</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>456587</t>
+          <t>496888</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>512023</t>
+          <t>557636</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,53%</t>
         </is>
       </c>
     </row>
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>133692</t>
+          <t>138486</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113326</t>
+          <t>117939</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155138</t>
+          <t>161331</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8296,22 +8296,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>115207</t>
+          <t>128695</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102348</t>
+          <t>113209</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132469</t>
+          <t>146222</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>248899</t>
+          <t>267180</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>224472</t>
+          <t>239530</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>275419</t>
+          <t>296886</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -8374,17 +8374,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8409,17 +8409,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8444,17 +8444,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8491,32 +8491,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42894</t>
+          <t>48685</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14679</t>
+          <t>36041</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75259</t>
+          <t>64202</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8526,32 +8526,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22171</t>
+          <t>26890</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>19258</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31514</t>
+          <t>36007</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8561,32 +8561,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>65065</t>
+          <t>75575</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24989</t>
+          <t>59544</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>96620</t>
+          <t>93511</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -8604,32 +8604,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>277952</t>
+          <t>310575</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>108902</t>
+          <t>288391</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>449218</t>
+          <t>332102</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8639,32 +8639,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>105583</t>
+          <t>117289</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94605</t>
+          <t>105205</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115216</t>
+          <t>127780</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8674,32 +8674,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>383535</t>
+          <t>427864</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>177102</t>
+          <t>404880</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>550842</t>
+          <t>453188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>68,76%</t>
         </is>
       </c>
     </row>
@@ -8717,32 +8717,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>347418</t>
+          <t>112352</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150310</t>
+          <t>92510</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>539352</t>
+          <t>131654</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8752,32 +8752,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>39157</t>
+          <t>43318</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30422</t>
+          <t>33981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49387</t>
+          <t>54448</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8787,32 +8787,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>386575</t>
+          <t>155670</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>193857</t>
+          <t>133966</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>632451</t>
+          <t>177348</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -8830,17 +8830,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8865,17 +8865,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8900,17 +8900,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8947,32 +8947,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>123577</t>
+          <t>142499</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>102175</t>
+          <t>120291</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>152624</t>
+          <t>171628</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8982,32 +8982,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>89999</t>
+          <t>113731</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49755</t>
+          <t>97806</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119788</t>
+          <t>132830</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9017,32 +9017,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>213576</t>
+          <t>256230</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>148837</t>
+          <t>227322</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>255229</t>
+          <t>286701</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -9060,32 +9060,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>709875</t>
+          <t>760465</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>676989</t>
+          <t>722232</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>743503</t>
+          <t>794611</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9095,32 +9095,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>705295</t>
+          <t>547976</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>624252</t>
+          <t>525683</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>819341</t>
+          <t>572292</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9130,32 +9130,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1415170</t>
+          <t>1308442</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1329650</t>
+          <t>1263238</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1615113</t>
+          <t>1346885</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>67,62%</t>
         </is>
       </c>
     </row>
@@ -9173,32 +9173,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>200347</t>
+          <t>227793</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>176592</t>
+          <t>200401</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>231499</t>
+          <t>258742</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9208,32 +9208,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182800</t>
+          <t>199504</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>102609</t>
+          <t>178801</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>242045</t>
+          <t>221111</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9243,32 +9243,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>383147</t>
+          <t>427297</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>252040</t>
+          <t>393435</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>440962</t>
+          <t>467413</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -9286,17 +9286,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1033799</t>
+          <t>1130757</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1033799</t>
+          <t>1130757</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1033799</t>
+          <t>1130757</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9321,17 +9321,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9356,17 +9356,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2011893</t>
+          <t>1991969</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2011893</t>
+          <t>1991969</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2011893</t>
+          <t>1991969</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9403,32 +9403,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>62822</t>
+          <t>97552</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48915</t>
+          <t>80886</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>79190</t>
+          <t>116548</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9438,32 +9438,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>146525</t>
+          <t>96767</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>79463</t>
+          <t>81388</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>328806</t>
+          <t>111712</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9473,32 +9473,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>209348</t>
+          <t>194319</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>140223</t>
+          <t>167860</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>398304</t>
+          <t>218643</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -9516,32 +9516,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>334923</t>
+          <t>388357</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>311427</t>
+          <t>363344</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>356162</t>
+          <t>414061</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9551,32 +9551,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>575198</t>
+          <t>606898</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>427557</t>
+          <t>584693</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>637030</t>
+          <t>626910</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9586,32 +9586,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>910120</t>
+          <t>995255</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>756188</t>
+          <t>963920</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>972591</t>
+          <t>1026436</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,38%</t>
         </is>
       </c>
     </row>
@@ -9629,32 +9629,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>77301</t>
+          <t>82055</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60806</t>
+          <t>63565</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96817</t>
+          <t>101937</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9664,32 +9664,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>119612</t>
+          <t>127186</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>89182</t>
+          <t>111302</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>143494</t>
+          <t>144782</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9699,17 +9699,17 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>196913</t>
+          <t>209240</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>159081</t>
+          <t>185096</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>225742</t>
+          <t>237813</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -9742,17 +9742,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9777,17 +9777,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9812,17 +9812,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9844,7 +9844,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9859,32 +9859,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25647</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11470</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47585</t>
+          <t>45067</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9894,32 +9894,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>76916</t>
+          <t>89492</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62445</t>
+          <t>73615</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>96345</t>
+          <t>108184</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9929,32 +9929,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>102562</t>
+          <t>113213</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>82653</t>
+          <t>92353</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>130642</t>
+          <t>138725</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -9972,32 +9972,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>152206</t>
+          <t>158417</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>124871</t>
+          <t>134324</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>176736</t>
+          <t>181413</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10007,32 +10007,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>546493</t>
+          <t>606664</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>521280</t>
+          <t>580037</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>568104</t>
+          <t>633421</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10042,32 +10042,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>698699</t>
+          <t>765082</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>658976</t>
+          <t>727023</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>731294</t>
+          <t>797992</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>73,79%</t>
         </is>
       </c>
     </row>
@@ -10085,32 +10085,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>62654</t>
+          <t>55089</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>40197</t>
+          <t>37946</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>89668</t>
+          <t>77997</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10120,32 +10120,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>137962</t>
+          <t>148125</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>119134</t>
+          <t>125691</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>161144</t>
+          <t>171818</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10155,32 +10155,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>200617</t>
+          <t>203214</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>172887</t>
+          <t>174492</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>237906</t>
+          <t>236079</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -10198,17 +10198,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10233,17 +10233,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10268,17 +10268,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10315,32 +10315,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>348329</t>
+          <t>421360</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>270136</t>
+          <t>379077</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>399871</t>
+          <t>465344</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10350,17 +10350,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>435431</t>
+          <t>442443</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>346688</t>
+          <t>407623</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>652182</t>
+          <t>481198</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10385,32 +10385,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>783760</t>
+          <t>863803</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>672794</t>
+          <t>810313</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1022303</t>
+          <t>918141</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -10428,32 +10428,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2005606</t>
+          <t>2193318</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1469360</t>
+          <t>2126990</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2182380</t>
+          <t>2257061</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10463,32 +10463,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2374681</t>
+          <t>2362815</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2239624</t>
+          <t>2312163</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2581603</t>
+          <t>2411645</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10498,32 +10498,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4380287</t>
+          <t>4556133</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3866212</t>
+          <t>4473569</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4631363</t>
+          <t>4635289</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>65,5%</t>
         </is>
       </c>
     </row>
@@ -10541,32 +10541,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1021106</t>
+          <t>826712</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>817937</t>
+          <t>769381</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1675803</t>
+          <t>886278</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10576,32 +10576,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>767646</t>
+          <t>830135</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>626459</t>
+          <t>788317</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>839906</t>
+          <t>878904</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10611,32 +10611,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1788751</t>
+          <t>1656847</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1558119</t>
+          <t>1588956</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2442575</t>
+          <t>1731358</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -10654,17 +10654,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3375041</t>
+          <t>3441390</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3375041</t>
+          <t>3441390</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3375041</t>
+          <t>3441390</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10689,17 +10689,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10724,17 +10724,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6952798</t>
+          <t>7076783</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6952798</t>
+          <t>7076783</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6952798</t>
+          <t>7076783</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
